--- a/xlsx/Power/p20.xlsx
+++ b/xlsx/Power/p20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66618194-D0D1-49BF-8DCC-A21000EE81CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CC4365-2D82-44F9-BE01-D9DBC80F6DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FDAE93B6-84E1-487D-8768-1632AF37DF23}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FDAE93B6-84E1-487D-8768-1632AF37DF23}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.28799999999999998</v>
       </c>
       <c r="C1">
-        <v>0.52700000000000002</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="D1">
-        <v>0.71299999999999997</v>
+        <v>0.17</v>
       </c>
       <c r="E1">
-        <v>0.82099999999999995</v>
+        <v>0.376</v>
       </c>
       <c r="F1">
-        <v>0.90400000000000003</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="G1">
-        <v>0.97599999999999998</v>
+        <v>0.86499999999999999</v>
       </c>
       <c r="H1">
-        <v>0.98699999999999999</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="I1">
-        <v>0.995</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="J1">
-        <v>1</v>
+        <v>0.99099999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="C2">
-        <v>0.374</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="D2">
-        <v>0.56999999999999995</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="E2">
-        <v>0.66</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="F2">
-        <v>0.80900000000000005</v>
+        <v>0.51</v>
       </c>
       <c r="G2">
-        <v>0.92800000000000005</v>
+        <v>0.71699999999999997</v>
       </c>
       <c r="H2">
-        <v>0.94799999999999995</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="I2">
-        <v>0.97599999999999998</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="J2">
-        <v>0.99199999999999999</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,22 +468,22 @@
         <v>0.25</v>
       </c>
       <c r="C3">
-        <v>0.437</v>
+        <v>0.504</v>
       </c>
       <c r="D3">
-        <v>0.59599999999999997</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="E3">
-        <v>0.68500000000000005</v>
+        <v>0.69699999999999995</v>
       </c>
       <c r="F3">
-        <v>0.81</v>
+        <v>0.82</v>
       </c>
       <c r="G3">
         <v>0.91100000000000003</v>
       </c>
       <c r="H3">
-        <v>0.92700000000000005</v>
+        <v>0.92900000000000005</v>
       </c>
       <c r="I3">
         <v>0.94799999999999995</v>
@@ -494,34 +494,34 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.128</v>
+        <v>0.158</v>
       </c>
       <c r="B4">
-        <v>0.22700000000000001</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="C4">
-        <v>0.36799999999999999</v>
+        <v>0.377</v>
       </c>
       <c r="D4">
-        <v>0.499</v>
+        <v>0.497</v>
       </c>
       <c r="E4">
-        <v>0.57799999999999996</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="F4">
-        <v>0.70899999999999996</v>
+        <v>0.71099999999999997</v>
       </c>
       <c r="G4">
         <v>0.82299999999999995</v>
       </c>
       <c r="H4">
-        <v>0.84099999999999997</v>
+        <v>0.83899999999999997</v>
       </c>
       <c r="I4">
         <v>0.88100000000000001</v>
       </c>
       <c r="J4">
-        <v>0.93700000000000006</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="C6">
-        <v>0.10299999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="D6">
-        <v>0.16500000000000001</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="E6">
-        <v>0.193</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="F6">
-        <v>0.29699999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G6">
-        <v>0.47899999999999998</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="H6">
-        <v>0.64200000000000002</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="I6">
-        <v>0.75700000000000001</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="J6">
-        <v>0.83099999999999996</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.09</v>
       </c>
       <c r="C7">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D7">
-        <v>0.216</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="E7">
-        <v>0.29699999999999999</v>
+        <v>0.30099999999999999</v>
       </c>
       <c r="F7">
-        <v>0.40799999999999997</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="G7">
-        <v>0.58199999999999996</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="H7">
         <v>0.69199999999999995</v>
       </c>
       <c r="I7">
-        <v>0.81</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="J7">
-        <v>0.90200000000000002</v>
+        <v>0.89700000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.376</v>
       </c>
       <c r="C8">
-        <v>0.56899999999999995</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.74099999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="E8">
-        <v>0.80700000000000005</v>
+        <v>0.42299999999999999</v>
       </c>
       <c r="F8">
-        <v>0.88600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="G8">
-        <v>0.94</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="H8">
-        <v>0.96599999999999997</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="I8">
-        <v>0.99199999999999999</v>
+        <v>0.77900000000000003</v>
       </c>
       <c r="J8">
-        <v>0.999</v>
+        <v>0.85699999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.112</v>
       </c>
       <c r="C9">
-        <v>0.01</v>
+        <v>0.157</v>
       </c>
       <c r="D9">
-        <v>4.3999999999999997E-2</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="E9">
-        <v>0.17199999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="F9">
-        <v>0.26300000000000001</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="G9">
-        <v>0.29299999999999998</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="H9">
-        <v>0.34300000000000003</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="I9">
-        <v>0.42899999999999999</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="J9">
-        <v>0.45700000000000002</v>
+        <v>0.48699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p20.xlsx
+++ b/xlsx/Power/p20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CC4365-2D82-44F9-BE01-D9DBC80F6DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12314B2-7A67-4F53-AA46-328438549D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FDAE93B6-84E1-487D-8768-1632AF37DF23}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FDAE93B6-84E1-487D-8768-1632AF37DF23}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.28799999999999998</v>
       </c>
       <c r="C1">
-        <v>1.0999999999999999E-2</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="D1">
-        <v>0.17</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="E1">
-        <v>0.376</v>
+        <v>0.82099999999999995</v>
       </c>
       <c r="F1">
-        <v>0.66800000000000004</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="G1">
-        <v>0.86499999999999999</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="H1">
-        <v>0.92400000000000004</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="I1">
-        <v>0.96599999999999997</v>
+        <v>0.995</v>
       </c>
       <c r="J1">
-        <v>0.99099999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="C2">
-        <v>8.0000000000000002E-3</v>
+        <v>0.374</v>
       </c>
       <c r="D2">
-        <v>9.8000000000000004E-2</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="E2">
-        <v>0.26500000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="F2">
-        <v>0.51</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="G2">
-        <v>0.71699999999999997</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="H2">
-        <v>0.82499999999999996</v>
+        <v>0.94799999999999995</v>
       </c>
       <c r="I2">
-        <v>0.91300000000000003</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="J2">
-        <v>0.96299999999999997</v>
+        <v>0.99199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,22 +468,22 @@
         <v>0.25</v>
       </c>
       <c r="C3">
-        <v>0.504</v>
+        <v>0.437</v>
       </c>
       <c r="D3">
-        <v>0.61799999999999999</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="E3">
-        <v>0.69699999999999995</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="F3">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="G3">
         <v>0.91100000000000003</v>
       </c>
       <c r="H3">
-        <v>0.92900000000000005</v>
+        <v>0.92700000000000005</v>
       </c>
       <c r="I3">
         <v>0.94799999999999995</v>
@@ -494,34 +494,34 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.158</v>
+        <v>0.129</v>
       </c>
       <c r="B4">
-        <v>0.24299999999999999</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="C4">
-        <v>0.377</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="D4">
-        <v>0.497</v>
+        <v>0.499</v>
       </c>
       <c r="E4">
-        <v>0.58099999999999996</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="F4">
-        <v>0.71099999999999997</v>
+        <v>0.70899999999999996</v>
       </c>
       <c r="G4">
         <v>0.82299999999999995</v>
       </c>
       <c r="H4">
-        <v>0.83899999999999997</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="I4">
         <v>0.88100000000000001</v>
       </c>
       <c r="J4">
-        <v>0.94</v>
+        <v>0.93700000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="C6">
-        <v>0.44</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="D6">
-        <v>0.29099999999999998</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="E6">
-        <v>0.29099999999999998</v>
+        <v>0.193</v>
       </c>
       <c r="F6">
-        <v>0.39</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="G6">
-        <v>0.52500000000000002</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="H6">
-        <v>0.67700000000000005</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="I6">
-        <v>0.77700000000000002</v>
+        <v>0.755</v>
       </c>
       <c r="J6">
-        <v>0.876</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.09</v>
       </c>
       <c r="C7">
-        <v>0.14000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="D7">
-        <v>0.21299999999999999</v>
+        <v>0.216</v>
       </c>
       <c r="E7">
-        <v>0.30099999999999999</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="F7">
-        <v>0.39800000000000002</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="G7">
-        <v>0.55100000000000005</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="H7">
         <v>0.69199999999999995</v>
       </c>
       <c r="I7">
-        <v>0.79900000000000004</v>
+        <v>0.81</v>
       </c>
       <c r="J7">
-        <v>0.89700000000000002</v>
+        <v>0.90200000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.376</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="D8">
-        <v>0.22</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="E8">
-        <v>0.42299999999999999</v>
+        <v>0.80700000000000005</v>
       </c>
       <c r="F8">
-        <v>0.67</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="G8">
-        <v>0.81200000000000006</v>
+        <v>0.94</v>
       </c>
       <c r="H8">
-        <v>0.89500000000000002</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="I8">
-        <v>0.77900000000000003</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="J8">
-        <v>0.85699999999999998</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.112</v>
       </c>
       <c r="C9">
-        <v>0.157</v>
+        <v>0.01</v>
       </c>
       <c r="D9">
-        <v>0.82499999999999996</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="E9">
-        <v>0.74</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="F9">
-        <v>0.44900000000000001</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="G9">
-        <v>0.39300000000000002</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="H9">
-        <v>0.39700000000000002</v>
+        <v>0.34300000000000003</v>
       </c>
       <c r="I9">
+        <v>0.42899999999999999</v>
+      </c>
+      <c r="J9">
         <v>0.45700000000000002</v>
-      </c>
-      <c r="J9">
-        <v>0.48699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p20.xlsx
+++ b/xlsx/Power/p20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12314B2-7A67-4F53-AA46-328438549D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C8E595-F99C-42C1-9D7F-3C0E8ECF2315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FDAE93B6-84E1-487D-8768-1632AF37DF23}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{FDAE93B6-84E1-487D-8768-1632AF37DF23}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,22 +398,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.13300000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="B1">
         <v>0.28799999999999998</v>
       </c>
       <c r="C1">
-        <v>0.52700000000000002</v>
+        <v>0.53</v>
       </c>
       <c r="D1">
-        <v>0.71299999999999997</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="E1">
-        <v>0.82099999999999995</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="F1">
-        <v>0.90400000000000003</v>
+        <v>0.90500000000000003</v>
       </c>
       <c r="G1">
         <v>0.97599999999999998</v>
@@ -422,7 +422,7 @@
         <v>0.98699999999999999</v>
       </c>
       <c r="I1">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
       <c r="J1">
         <v>1</v>
@@ -430,31 +430,31 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.114</v>
+        <v>0.112</v>
       </c>
       <c r="B2">
-        <v>0.19800000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="C2">
-        <v>0.374</v>
+        <v>0.378</v>
       </c>
       <c r="D2">
-        <v>0.56999999999999995</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="E2">
-        <v>0.66</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="F2">
         <v>0.80900000000000005</v>
       </c>
       <c r="G2">
-        <v>0.92800000000000005</v>
+        <v>0.92700000000000005</v>
       </c>
       <c r="H2">
-        <v>0.94799999999999995</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="I2">
-        <v>0.97599999999999998</v>
+        <v>0.97799999999999998</v>
       </c>
       <c r="J2">
         <v>0.99199999999999999</v>
@@ -462,98 +462,98 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.13400000000000001</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="B3">
         <v>0.25</v>
       </c>
       <c r="C3">
-        <v>0.437</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="D3">
         <v>0.59599999999999997</v>
       </c>
       <c r="E3">
-        <v>0.68500000000000005</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="F3">
-        <v>0.81</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="G3">
-        <v>0.91100000000000003</v>
+        <v>0.91200000000000003</v>
       </c>
       <c r="H3">
-        <v>0.92700000000000005</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="I3">
-        <v>0.94799999999999995</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="J3">
-        <v>0.98</v>
+        <v>0.98099999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="B4">
-        <v>0.22700000000000001</v>
+        <v>0.22900000000000001</v>
       </c>
       <c r="C4">
-        <v>0.36799999999999999</v>
+        <v>0.374</v>
       </c>
       <c r="D4">
-        <v>0.499</v>
+        <v>0.501</v>
       </c>
       <c r="E4">
-        <v>0.57799999999999996</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="F4">
-        <v>0.70899999999999996</v>
+        <v>0.71099999999999997</v>
       </c>
       <c r="G4">
         <v>0.82299999999999995</v>
       </c>
       <c r="H4">
-        <v>0.84099999999999997</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="I4">
-        <v>0.88100000000000001</v>
+        <v>0.88800000000000001</v>
       </c>
       <c r="J4">
-        <v>0.93700000000000006</v>
+        <v>0.94399999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4.7E-2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.10199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -567,25 +567,25 @@
         <v>0.10299999999999999</v>
       </c>
       <c r="D6">
-        <v>0.16500000000000001</v>
+        <v>0.158</v>
       </c>
       <c r="E6">
-        <v>0.193</v>
+        <v>0.186</v>
       </c>
       <c r="F6">
-        <v>0.29699999999999999</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="G6">
-        <v>0.47899999999999998</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="H6">
-        <v>0.64200000000000002</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="I6">
-        <v>0.755</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="J6">
-        <v>0.83</v>
+        <v>0.84199999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -593,22 +593,22 @@
         <v>6.3E-2</v>
       </c>
       <c r="B7">
-        <v>0.09</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="C7">
-        <v>0.15</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="D7">
-        <v>0.216</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="E7">
         <v>0.29699999999999999</v>
       </c>
       <c r="F7">
-        <v>0.40699999999999997</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="G7">
-        <v>0.58199999999999996</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="H7">
         <v>0.69199999999999995</v>
@@ -617,7 +617,7 @@
         <v>0.81</v>
       </c>
       <c r="J7">
-        <v>0.90200000000000002</v>
+        <v>0.90100000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -625,19 +625,19 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="B8">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="C8">
         <v>0.56899999999999995</v>
       </c>
       <c r="D8">
-        <v>0.74099999999999999</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="E8">
-        <v>0.80700000000000005</v>
+        <v>0.80800000000000005</v>
       </c>
       <c r="F8">
-        <v>0.88600000000000001</v>
+        <v>0.88700000000000001</v>
       </c>
       <c r="G8">
         <v>0.94</v>
@@ -657,7 +657,7 @@
         <v>7.8E-2</v>
       </c>
       <c r="B9">
-        <v>0.112</v>
+        <v>0.114</v>
       </c>
       <c r="C9">
         <v>0.01</v>
@@ -666,22 +666,22 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="E9">
-        <v>0.17199999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="F9">
-        <v>0.26300000000000001</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="G9">
-        <v>0.29299999999999998</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H9">
-        <v>0.34300000000000003</v>
+        <v>0.34399999999999997</v>
       </c>
       <c r="I9">
-        <v>0.42899999999999999</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="J9">
-        <v>0.45700000000000002</v>
+        <v>0.46500000000000002</v>
       </c>
     </row>
   </sheetData>
